--- a/VT_REG1_TRA_V12.xlsx
+++ b/VT_REG1_TRA_V12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\001_Academic\002_Course_Works\003_2026_Sping_Semester\003_Low-Carbon Technologies and Policies\000_ICP_BL\006_Cambodia_TIMES_Model_V002\KHM_TIMES_V002_20260603\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serey\Downloads\Cambodia-TIMES-Model-main\Cambodia-TIMES-Model-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC28FFD-1ED6-4AB5-8162-A90BCD410E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DDE7F7-6DC8-4F07-A989-768FBDD4224D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -28,6 +28,19 @@
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2808,7 +2821,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="28" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3101,6 +3114,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="24">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -5051,21 +5065,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA37"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="21" width="10.88671875" customWidth="1"/>
-    <col min="22" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
       <c r="X1" s="20" t="s">
         <v>93</v>
       </c>
@@ -5079,7 +5093,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D2" s="38" t="s">
         <v>44</v>
       </c>
@@ -5147,7 +5161,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="2:27" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" ht="38.25" x14ac:dyDescent="0.2">
       <c r="C3" s="58" t="s">
         <v>122</v>
       </c>
@@ -5209,7 +5223,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B4" s="36"/>
       <c r="C4" s="75" t="s">
         <v>57</v>
@@ -5234,7 +5248,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="76"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B5" s="40" t="s">
         <v>58</v>
       </c>
@@ -5318,7 +5332,7 @@
         <v>53.616579479999999</v>
       </c>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B6" s="40" t="s">
         <v>60</v>
       </c>
@@ -5402,7 +5416,7 @@
         <v>17.352778751999999</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B7" s="40" t="s">
         <v>62</v>
       </c>
@@ -5486,7 +5500,7 @@
         <v>105.16278636</v>
       </c>
     </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B8" s="40" t="s">
         <v>64</v>
       </c>
@@ -5570,7 +5584,7 @@
         <v>8.9932882680000006</v>
       </c>
     </row>
-    <row r="9" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="40" t="s">
         <v>66</v>
       </c>
@@ -5654,7 +5668,7 @@
         <v>101.39634108000001</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B10" s="40" t="s">
         <v>68</v>
       </c>
@@ -5738,7 +5752,7 @@
         <v>9.4588185599999992</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B11" s="40" t="s">
         <v>86</v>
       </c>
@@ -5822,7 +5836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B12" s="40" t="s">
         <v>87</v>
       </c>
@@ -5906,7 +5920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
         <v>89</v>
       </c>
@@ -5981,7 +5995,7 @@
         <v>295.9805925</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -5992,7 +6006,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -6003,7 +6017,7 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="C16" s="44" t="s">
         <v>152</v>
       </c>
@@ -6018,7 +6032,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -6029,7 +6043,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -6040,7 +6054,7 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -6051,7 +6065,7 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -6062,7 +6076,7 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -6073,7 +6087,7 @@
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -6084,11 +6098,11 @@
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1"/>
       <c r="D23" s="21"/>
     </row>
-    <row r="24" spans="2:24" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" ht="38.25" x14ac:dyDescent="0.2">
       <c r="B24" s="22" t="s">
         <v>102</v>
       </c>
@@ -6153,7 +6167,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
         <v>66</v>
       </c>
@@ -6171,11 +6185,13 @@
         <v>0.12</v>
       </c>
       <c r="J25" s="88">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
       <c r="K25" s="85"/>
       <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
+      <c r="M25" s="88">
+        <v>0.5</v>
+      </c>
       <c r="N25" s="85"/>
       <c r="O25" s="85"/>
       <c r="P25" s="85"/>
@@ -6189,7 +6205,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
         <v>66</v>
       </c>
@@ -6223,7 +6239,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="27" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
         <v>66</v>
       </c>
@@ -6239,11 +6255,13 @@
         <v>0</v>
       </c>
       <c r="J27" s="116">
-        <v>0.74</v>
+        <v>0.45</v>
       </c>
       <c r="K27" s="115"/>
       <c r="L27" s="115"/>
-      <c r="M27" s="115"/>
+      <c r="M27" s="116">
+        <v>0.45</v>
+      </c>
       <c r="N27" s="115"/>
       <c r="O27" s="115"/>
       <c r="P27" s="115"/>
@@ -6257,7 +6275,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="28" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
         <v>66</v>
       </c>
@@ -6277,7 +6295,9 @@
       </c>
       <c r="K28" s="115"/>
       <c r="L28" s="115"/>
-      <c r="M28" s="115"/>
+      <c r="M28" s="116">
+        <v>0.05</v>
+      </c>
       <c r="N28" s="115"/>
       <c r="O28" s="115"/>
       <c r="P28" s="115"/>
@@ -6291,7 +6311,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B29" s="40" t="s">
         <v>66</v>
       </c>
@@ -6325,7 +6345,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="40" t="s">
         <v>66</v>
       </c>
@@ -6361,7 +6381,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="40" t="s">
         <v>66</v>
       </c>
@@ -6378,7 +6398,9 @@
       <c r="I31" s="115"/>
       <c r="J31" s="115"/>
       <c r="K31" s="115"/>
-      <c r="L31" s="115"/>
+      <c r="L31" s="116">
+        <v>1</v>
+      </c>
       <c r="M31" s="115"/>
       <c r="N31" s="115"/>
       <c r="O31" s="115"/>
@@ -6393,7 +6415,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="32" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B32" s="40" t="s">
         <v>66</v>
       </c>
@@ -6409,11 +6431,13 @@
       <c r="H32" s="115"/>
       <c r="I32" s="115"/>
       <c r="J32" s="116">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="K32" s="115"/>
       <c r="L32" s="115"/>
-      <c r="M32" s="115"/>
+      <c r="M32" s="116">
+        <v>0</v>
+      </c>
       <c r="N32" s="115"/>
       <c r="O32" s="115"/>
       <c r="P32" s="115"/>
@@ -6427,7 +6451,29 @@
         <v>192</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="G34" s="158">
+        <f>SUM(G25:G32)</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="158">
+        <f t="shared" ref="H34:J34" si="2">SUM(H25:H32)</f>
+        <v>1</v>
+      </c>
+      <c r="I34" s="158">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J34" s="158">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="M34" s="158">
+        <f t="shared" ref="M34" si="3">SUM(M25:M32)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="55" t="s">
         <v>106</v>
       </c>
@@ -6438,7 +6484,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B36" s="20" t="s">
         <v>117</v>
       </c>
@@ -6452,7 +6498,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="40" t="s">
         <v>66</v>
       </c>
@@ -6472,19 +6518,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:G5"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.88671875" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="1" max="1" width="1.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="68" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="D5" s="69" t="s">
         <v>161</v>
       </c>
@@ -6502,29 +6548,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R37"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -6545,7 +6591,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B9</f>
         <v>TRA</v>
@@ -6581,7 +6627,7 @@
       <c r="Q2" s="106"/>
       <c r="R2" s="106"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="107" t="s">
         <v>7</v>
       </c>
@@ -6610,7 +6656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -6644,7 +6690,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="67"/>
@@ -6670,7 +6716,7 @@
       <c r="Q5" s="110"/>
       <c r="R5" s="110"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="67"/>
@@ -6694,7 +6740,7 @@
       <c r="Q6" s="110"/>
       <c r="R6" s="110"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="67"/>
@@ -6718,7 +6764,7 @@
       <c r="Q7" s="110"/>
       <c r="R7" s="110"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="67"/>
@@ -6742,7 +6788,7 @@
       <c r="Q8" s="110"/>
       <c r="R8" s="110"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="67"/>
@@ -6766,7 +6812,7 @@
       <c r="Q9" s="110"/>
       <c r="R9" s="110"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="67"/>
@@ -6794,7 +6840,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L11" s="110" t="str">
         <f>$B$2&amp;'EB1'!$H$2</f>
         <v>TRAKER</v>
@@ -6808,12 +6854,12 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L12" s="110"/>
       <c r="M12" s="111"/>
       <c r="N12" s="110"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D13" s="5" t="s">
         <v>13</v>
       </c>
@@ -6831,7 +6877,7 @@
       <c r="Q13" s="110"/>
       <c r="R13" s="110"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B14" s="17" t="s">
         <v>1</v>
       </c>
@@ -6881,7 +6927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:18" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="16" t="s">
         <v>39</v>
       </c>
@@ -6931,7 +6977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>91</v>
       </c>
@@ -6958,7 +7004,7 @@
       <c r="Q16" s="112"/>
       <c r="R16" s="112"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f t="shared" ref="B17:B23" si="1">L17</f>
         <v>FTE-TRAGAS</v>
@@ -7003,7 +7049,7 @@
       <c r="Q17" s="110"/>
       <c r="R17" s="110"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRADSL</v>
@@ -7046,7 +7092,7 @@
       <c r="Q18" s="110"/>
       <c r="R18" s="110"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRALPG</v>
@@ -7089,7 +7135,7 @@
       <c r="Q19" s="110"/>
       <c r="R19" s="110"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRAGSL</v>
@@ -7132,7 +7178,7 @@
       <c r="Q20" s="110"/>
       <c r="R20" s="110"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRABIO</v>
@@ -7175,7 +7221,7 @@
       <c r="Q21" s="110"/>
       <c r="R21" s="110"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRAELC</v>
@@ -7220,7 +7266,7 @@
       <c r="Q22" s="110"/>
       <c r="R22" s="110"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>FTE-TRAKER</v>
@@ -7262,14 +7308,14 @@
       <c r="Q23" s="110"/>
       <c r="R23" s="110"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
       <c r="G24" s="67"/>
       <c r="H24" s="11"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" s="23"/>
       <c r="D25" s="23"/>
       <c r="E25" s="12"/>
@@ -7278,7 +7324,7 @@
       <c r="H25" s="11"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="12"/>
@@ -7289,7 +7335,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="23"/>
       <c r="D27" s="23"/>
       <c r="E27" s="90"/>
@@ -7300,7 +7346,7 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B28" s="23"/>
       <c r="D28" s="23"/>
       <c r="E28" s="90"/>
@@ -7311,7 +7357,7 @@
       <c r="K28" s="23"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="90"/>
@@ -7320,7 +7366,7 @@
       <c r="H29" s="11"/>
       <c r="M29" s="19"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="90"/>
@@ -7328,7 +7374,7 @@
       <c r="G30" s="67"/>
       <c r="H30" s="11"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="12"/>
@@ -7336,7 +7382,7 @@
       <c r="G31" s="67"/>
       <c r="H31" s="11"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="12"/>
@@ -7344,13 +7390,13 @@
       <c r="G32" s="67"/>
       <c r="H32" s="11"/>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B36" s="42"/>
       <c r="C36" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B37" s="61"/>
       <c r="C37" s="1" t="s">
         <v>155</v>
@@ -7367,34 +7413,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:W39"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" customWidth="1"/>
-    <col min="11" max="11" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" customWidth="1"/>
-    <col min="16" max="16" width="7.109375" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="63.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.6640625" customWidth="1"/>
+    <col min="18" max="18" width="63.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.7109375" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" customWidth="1"/>
     <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -7418,7 +7464,7 @@
       </c>
       <c r="I1" s="27"/>
     </row>
-    <row r="2" spans="2:23" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="str">
         <f>'EB1'!B9</f>
         <v>TRA</v>
@@ -7457,7 +7503,7 @@
       <c r="V2" s="106"/>
       <c r="W2" s="106"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
       <c r="O3" s="107" t="s">
         <v>7</v>
       </c>
@@ -7486,7 +7532,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:23" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:23" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -7520,7 +7566,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -7546,7 +7592,7 @@
       <c r="V5" s="106"/>
       <c r="W5" s="106"/>
     </row>
-    <row r="6" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -7570,7 +7616,7 @@
       <c r="V6" s="106"/>
       <c r="W6" s="106"/>
     </row>
-    <row r="7" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -7594,7 +7640,7 @@
       <c r="V7" s="106"/>
       <c r="W7" s="106"/>
     </row>
-    <row r="8" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -7618,7 +7664,7 @@
       <c r="V8" s="106"/>
       <c r="W8" s="106"/>
     </row>
-    <row r="9" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
@@ -7642,7 +7688,7 @@
       <c r="V9" s="106"/>
       <c r="W9" s="106"/>
     </row>
-    <row r="10" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -7666,7 +7712,7 @@
       <c r="V10" s="106"/>
       <c r="W10" s="106"/>
     </row>
-    <row r="11" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -7690,13 +7736,13 @@
       <c r="V11" s="106"/>
       <c r="W11" s="106"/>
     </row>
-    <row r="12" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="157">
         <f>SUM(E24:E24)</f>
-        <v>3008.2425758174118</v>
+        <v>2134.2261517623533</v>
       </c>
       <c r="F12" s="9"/>
       <c r="O12" s="106"/>
@@ -7717,7 +7763,7 @@
       <c r="V12" s="106"/>
       <c r="W12" s="106"/>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E13" s="156"/>
       <c r="O13" s="110" t="s">
         <v>105</v>
@@ -7740,7 +7786,7 @@
       <c r="V13" s="110"/>
       <c r="W13" s="110"/>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="D15" s="5" t="s">
         <v>13</v>
       </c>
@@ -7760,7 +7806,7 @@
       <c r="V15" s="110"/>
       <c r="W15" s="110"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B16" s="17" t="s">
         <v>1</v>
       </c>
@@ -7823,7 +7869,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:23" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:23" ht="34.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="16" t="s">
         <v>39</v>
       </c>
@@ -7886,7 +7932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="2:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>91</v>
       </c>
@@ -7931,7 +7977,7 @@
       <c r="V18" s="109"/>
       <c r="W18" s="109"/>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" s="127" t="str">
         <f t="shared" ref="B19:B23" si="0">Q19</f>
         <v>TCAREDSL</v>
@@ -7955,20 +8001,20 @@
         <v>16.5</v>
       </c>
       <c r="H19" s="140">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="I19" s="64">
         <v>0.16</v>
       </c>
       <c r="J19" s="153">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K19" s="66">
         <v>1E-3</v>
       </c>
       <c r="M19" s="126">
         <f t="shared" ref="M19:M21" si="3">E19*G19*K19*H19</f>
-        <v>7.7265729901911602</v>
+        <v>6.4388108251593001</v>
       </c>
       <c r="O19" s="106" t="s">
         <v>97</v>
@@ -7995,7 +8041,7 @@
       </c>
       <c r="W19" s="110"/>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B20" s="130" t="str">
         <f t="shared" si="0"/>
         <v>TCARELPG</v>
@@ -8019,20 +8065,20 @@
         <v>14</v>
       </c>
       <c r="H20" s="140">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="I20" s="65">
         <v>0.16</v>
       </c>
       <c r="J20" s="153">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K20" s="66">
         <v>1E-3</v>
       </c>
       <c r="M20" s="126">
         <f t="shared" si="3"/>
-        <v>8.5297138814879991E-2</v>
+        <v>7.1080949012400002E-2</v>
       </c>
       <c r="O20" s="106" t="s">
         <v>97</v>
@@ -8059,7 +8105,7 @@
       </c>
       <c r="W20" s="110"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" s="132" t="str">
         <f t="shared" si="0"/>
         <v>TCAREGSL</v>
@@ -8074,29 +8120,29 @@
       </c>
       <c r="E21" s="60">
         <f>('EB1'!J$9*'EB1'!$J$25*F21/(K21*G21))*1.01</f>
-        <v>238.87425624073049</v>
+        <v>500.78460427826104</v>
       </c>
       <c r="F21" s="147">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="G21" s="151">
         <v>11.5</v>
       </c>
       <c r="H21" s="140">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="I21" s="64">
         <v>0.15</v>
       </c>
       <c r="J21" s="153">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K21" s="66">
         <v>1E-3</v>
       </c>
       <c r="M21" s="126">
         <f t="shared" si="3"/>
-        <v>4.1205809201526016</v>
+        <v>7.1987786865000025</v>
       </c>
       <c r="O21" s="106" t="s">
         <v>97</v>
@@ -8123,7 +8169,7 @@
       </c>
       <c r="W21" s="110"/>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" s="127" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEDSL</v>
@@ -8187,7 +8233,7 @@
       </c>
       <c r="W22" s="110"/>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" s="132" t="str">
         <f t="shared" si="0"/>
         <v>TPUBELPG</v>
@@ -8251,7 +8297,7 @@
       </c>
       <c r="W23" s="110"/>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B24" s="135" t="str">
         <f t="shared" ref="B24" si="7">Q24</f>
         <v>TMOTEGSL</v>
@@ -8266,10 +8312,10 @@
       </c>
       <c r="E24" s="60">
         <f>('EB1'!J$9*'EB1'!$J$27*F24/(K24*G24))*1.01</f>
-        <v>3008.2425758174118</v>
+        <v>2134.2261517623533</v>
       </c>
       <c r="F24" s="148">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G24" s="153">
         <v>8.5</v>
@@ -8288,7 +8334,7 @@
       </c>
       <c r="M24" s="126">
         <f t="shared" ref="M24" si="10">E24*G24*K24*H24</f>
-        <v>31.962577368060003</v>
+        <v>22.676152862475007</v>
       </c>
       <c r="O24" s="106" t="s">
         <v>97</v>
@@ -8315,7 +8361,7 @@
       </c>
       <c r="W24" s="110"/>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B25" s="127" t="str">
         <f t="shared" ref="B25:B26" si="11">Q25</f>
         <v>TTRIELPG</v>
@@ -8379,7 +8425,7 @@
       </c>
       <c r="W25" s="110"/>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B26" s="132" t="str">
         <f t="shared" si="11"/>
         <v>TTRIEGSL</v>
@@ -8443,7 +8489,7 @@
       </c>
       <c r="W26" s="110"/>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B27" s="135" t="str">
         <f t="shared" ref="B27" si="15">Q27</f>
         <v>TFREEDSL</v>
@@ -8507,7 +8553,7 @@
       </c>
       <c r="W27" s="110"/>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B28" s="135" t="str">
         <f t="shared" ref="B28" si="18">Q28</f>
         <v>TAVIEKER</v>
@@ -8522,10 +8568,10 @@
       </c>
       <c r="E28" s="124">
         <f>('EB1'!H$9*'EB1'!$H$30*F28/(K28*G28))*1.01</f>
-        <v>30.226518864000006</v>
+        <v>9.067955659199999</v>
       </c>
       <c r="F28" s="141">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G28" s="91">
         <v>100</v>
@@ -8544,7 +8590,7 @@
       </c>
       <c r="M28" s="125">
         <f t="shared" ref="M28:M29" si="21">E28*G28*K28*H28</f>
-        <v>3.0226518864000003</v>
+        <v>0.90679556591999999</v>
       </c>
       <c r="O28" s="114" t="s">
         <v>97</v>
@@ -8571,7 +8617,7 @@
       </c>
       <c r="W28" s="113"/>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B29" s="135" t="str">
         <f t="shared" ref="B29" si="22">Q29</f>
         <v>TRAIEDSL</v>
@@ -8635,7 +8681,7 @@
       </c>
       <c r="W29" s="110"/>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B30" s="127" t="str">
         <f t="shared" ref="B30:B31" si="25">Q30</f>
         <v>TMAREDSL</v>
@@ -8699,7 +8745,7 @@
       </c>
       <c r="W30" s="110"/>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B31" t="str">
         <f t="shared" si="25"/>
         <v>TMAREGSL</v>
@@ -8714,7 +8760,7 @@
       </c>
       <c r="E31" s="60">
         <f>('EB1'!J$9*'EB1'!$J$32*F31/(K31*G31))*1.01</f>
-        <v>6.4789008178500005</v>
+        <v>0</v>
       </c>
       <c r="F31" s="65">
         <v>0.15</v>
@@ -8736,7 +8782,7 @@
       </c>
       <c r="M31" s="126">
         <f t="shared" ref="M31" si="28">E31*G31*K31*H31</f>
-        <v>0.12957801635700003</v>
+        <v>0</v>
       </c>
       <c r="O31" s="106" t="s">
         <v>97</v>
@@ -8763,7 +8809,7 @@
       </c>
       <c r="W31" s="110"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B34" s="42"/>
       <c r="C34" s="1" t="s">
         <v>154</v>
@@ -8772,7 +8818,7 @@
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B35" s="61"/>
       <c r="C35" s="1" t="s">
         <v>155</v>
@@ -8782,23 +8828,23 @@
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="E38" s="1"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="E39" s="1"/>
     </row>
   </sheetData>
@@ -8811,20 +8857,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:J40"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -8841,7 +8887,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>83</v>
       </c>
@@ -8856,7 +8902,7 @@
         <v>M$2021</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -8867,7 +8913,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>80</v>
       </c>
@@ -8893,7 +8939,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B7" s="16" t="s">
         <v>81</v>
       </c>
@@ -8915,7 +8961,7 @@
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="2:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
         <v>91</v>
       </c>
@@ -8932,7 +8978,7 @@
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>35</v>
       </c>
@@ -8945,7 +8991,7 @@
       </c>
       <c r="E9" s="59">
         <f>SUMIF(DemTechs_TRA!D$19:D$31,Demands!C9,DemTechs_TRA!M$19:M$31)</f>
-        <v>11.932451049158642</v>
+        <v>13.708670460671701</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>120</v>
@@ -8961,7 +9007,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -8990,7 +9036,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>35</v>
       </c>
@@ -9003,7 +9049,7 @@
       </c>
       <c r="E11" s="59">
         <f>SUMIF(DemTechs_TRA!D$19:D$31,Demands!C11,DemTechs_TRA!M$19:M$31)</f>
-        <v>31.962577368060003</v>
+        <v>22.676152862475007</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>120</v>
@@ -9019,7 +9065,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>35</v>
       </c>
@@ -9048,7 +9094,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -9077,7 +9123,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>35</v>
       </c>
@@ -9090,7 +9136,7 @@
       </c>
       <c r="E14" s="59">
         <f>SUMIF(DemTechs_TRA!D$19:D$31,Demands!C14,DemTechs_TRA!M$19:M$31)</f>
-        <v>3.0226518864000003</v>
+        <v>0.90679556591999999</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>120</v>
@@ -9106,7 +9152,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>35</v>
       </c>
@@ -9135,7 +9181,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>35</v>
       </c>
@@ -9148,7 +9194,7 @@
       </c>
       <c r="E16" s="59">
         <f>SUMIF(DemTechs_TRA!D$19:D$31,Demands!C16,DemTechs_TRA!M$19:M$31)</f>
-        <v>1.9243684902689999</v>
+        <v>1.794790473912</v>
       </c>
       <c r="G16" s="25" t="s">
         <v>120</v>
@@ -9164,7 +9210,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G17" s="1" t="s">
         <v>120</v>
       </c>
@@ -9179,7 +9225,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G18" s="1" t="s">
         <v>120</v>
       </c>
@@ -9194,7 +9240,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G19" s="1" t="s">
         <v>120</v>
       </c>
@@ -9209,7 +9255,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G20" s="25" t="s">
         <v>120</v>
       </c>
@@ -9224,7 +9270,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G21" s="1" t="s">
         <v>120</v>
       </c>
@@ -9239,7 +9285,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G22" s="1" t="s">
         <v>120</v>
       </c>
@@ -9254,7 +9300,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G23" s="1" t="s">
         <v>120</v>
       </c>
@@ -9269,7 +9315,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G24" s="25" t="s">
         <v>120</v>
       </c>
@@ -9284,7 +9330,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G25" s="1" t="s">
         <v>120</v>
       </c>
@@ -9299,7 +9345,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26" s="42"/>
       <c r="C26" s="1" t="s">
         <v>154</v>
@@ -9318,7 +9364,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27" s="61"/>
       <c r="C27" s="1" t="s">
         <v>155</v>
@@ -9337,7 +9383,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G28" s="25" t="s">
         <v>120</v>
       </c>
@@ -9352,7 +9398,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G29" s="1" t="s">
         <v>120</v>
       </c>
@@ -9367,7 +9413,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G30" s="1" t="s">
         <v>120</v>
       </c>
@@ -9382,7 +9428,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G31" s="1" t="s">
         <v>120</v>
       </c>
@@ -9397,7 +9443,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G32" s="25" t="s">
         <v>120</v>
       </c>
@@ -9412,7 +9458,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G33" s="1" t="s">
         <v>120</v>
       </c>
@@ -9427,7 +9473,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G34" s="1" t="s">
         <v>120</v>
       </c>
@@ -9442,7 +9488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G35" s="1" t="s">
         <v>120</v>
       </c>
@@ -9457,7 +9503,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G36" s="25" t="s">
         <v>120</v>
       </c>
@@ -9472,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G37" s="1" t="s">
         <v>120</v>
       </c>
@@ -9487,7 +9533,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="38" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G38" s="1" t="s">
         <v>120</v>
       </c>
@@ -9502,7 +9548,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G39" s="1" t="s">
         <v>120</v>
       </c>
@@ -9517,7 +9563,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="40" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:10" x14ac:dyDescent="0.2">
       <c r="G40" s="25" t="s">
         <v>120</v>
       </c>
@@ -9541,12 +9587,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:L24"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="32" t="s">
         <v>145</v>
       </c>
@@ -9557,7 +9603,7 @@
       <c r="G3" s="32"/>
       <c r="H3" s="32"/>
     </row>
-    <row r="4" spans="2:12" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="33"/>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
@@ -9565,13 +9611,13 @@
       <c r="F4" s="33"/>
       <c r="G4" s="33"/>
     </row>
-    <row r="5" spans="2:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="30" t="s">
         <v>146</v>
       </c>
       <c r="C5" s="31"/>
     </row>
-    <row r="6" spans="2:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="35" t="s">
         <v>0</v>
       </c>
@@ -9596,7 +9642,7 @@
       </c>
       <c r="H6" s="34"/>
     </row>
-    <row r="7" spans="2:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>91</v>
       </c>
@@ -9618,7 +9664,7 @@
       <c r="H7" s="95"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="34" t="str">
         <f>DemTechs_TRA!Q13</f>
         <v>TRACO2</v>
@@ -9641,16 +9687,16 @@
       <c r="H8" s="96"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="L10" s="1"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="42"/>
       <c r="C23" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="61"/>
       <c r="C24" s="1" t="s">
         <v>155</v>
